--- a/samples.xlsx
+++ b/samples.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\NLP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618C324E-F565-4FEA-A3B6-E1017699B8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9BC021-B5C6-4A9F-A204-5C1BD3F19663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -456,39 +456,12 @@
     <t>MR</t>
   </si>
   <si>
-    <t>可能漏写部位: 股动脉</t>
-  </si>
-  <si>
-    <t>可能漏写部位: 双肾上腺</t>
-  </si>
-  <si>
     <t>测量值['35cm']过大，请检查</t>
   </si>
   <si>
-    <t>请注意检查方式: 本检查无增强，但出现“脾脏形态、大小、密度未见明确异常,增强扫描未见异常强化灶”描述</t>
-  </si>
-  <si>
-    <t>请注意检查方式: 增强未描述</t>
-  </si>
-  <si>
-    <t>请注意检查方式: 弥散成像未描述</t>
-  </si>
-  <si>
-    <t>请注意检查方式: 磁敏感成像未描述</t>
-  </si>
-  <si>
-    <t>结论可能遗漏: 主动脉、冠状动脉硬化</t>
-  </si>
-  <si>
-    <t>结论可能遗漏: 胰管轻度扩张</t>
-  </si>
-  <si>
     <t>附见右侧甲状腺增大 中术语“右侧甲状腺”不标准</t>
   </si>
   <si>
-    <t>左肺下叶前基底段少许慢性炎症 中术语“左肺下叶前基底段”不标准；左肺下叶前基底段少许斑片影 中术语“左肺下叶前基底段”不标准</t>
-  </si>
-  <si>
     <t>双侧侧脑室旁白质及基底节区散在斑点状低密度灶,病灶内局部FLAIR序列呈低信号 中术语“密度”不标准</t>
   </si>
   <si>
@@ -498,55 +471,84 @@
     <t>左肺上叶前基底段一枚磨玻璃结节 中术语“上叶前基底段”不标准</t>
   </si>
   <si>
-    <t>危急值:肺栓塞</t>
-  </si>
-  <si>
-    <t>危急值:严重颅内出血</t>
-  </si>
-  <si>
     <t>男性报告中出现：女性附件</t>
   </si>
   <si>
-    <t>以下语言可能矛盾： 肝实质密度均匀,未见异常密度影；考虑多囊肝改变</t>
-  </si>
-  <si>
-    <t>以下语言可能矛盾： 肝脏形态正常；肝边缘欠光整</t>
-  </si>
-  <si>
-    <t>请注意检查方式: 增强未描述;结论可能遗漏: 肝左叶较小;以下语言可能矛盾： 肝脏未见异常密度影；肝左叶较小；双肾及肾上腺未见明显异常；附见右肾小囊肿</t>
-  </si>
-  <si>
-    <t>以下语言可能矛盾： 胰腺形态大小、密度未见异常；相邻胰腺头部略增大</t>
-  </si>
-  <si>
-    <t>以下语言可能矛盾： 右侧胸腔未见积液；右侧胸腔积液</t>
-  </si>
-  <si>
-    <t>以下描述与结论可能方位不符: [描述]左肺上叶前段另见钙化结节；[结论]右肺上叶前段钙化结节</t>
-  </si>
-  <si>
-    <t>以下描述与结论可能方位不符: [描述]右肺下叶前内基底段见不规则团片影；[结论]左肺下叶前内基底段不规则团片影</t>
-  </si>
-  <si>
-    <t>以下描述与结论可能方位不符: [描述]右髂窝见肾形软组织影伴钙化；[结论]左髂窝软组织影伴多发钙化</t>
-  </si>
-  <si>
-    <t>以下描述与结论可能方位不符: [描述]右肾上极见低密度影；[结论]左肾上极低密度灶</t>
-  </si>
-  <si>
     <t>缺少PI-RADS分类</t>
   </si>
   <si>
-    <t>以下描述与结论可能方位不符: [描述]左侧上颌骨内可见一不规则形高密度影；[结论]考虑右侧上颌骨占位性病变</t>
-  </si>
-  <si>
-    <t>结论可能遗漏: 门静脉左支可见一异常区域,大小强化约1CM,形态不规则,边界不清</t>
-  </si>
-  <si>
-    <t>可能漏写部位: 鼻窦;以下描述与结论可能方位不符: [描述]鼻腔左侧钩突(位于中鼻甲前上方的骨性突起)形态异常其尖端部分可见一局限性软组织密度影；[结论]鼻腔右侧钩突肥大并伴有软组织肿块</t>
-  </si>
-  <si>
     <t>applyTable</t>
+  </si>
+  <si>
+    <t>本检查无增强，但出现“脾脏形态、大小、密度未见明确异常,增强扫描未见异常强化灶”描述</t>
+  </si>
+  <si>
+    <t>增强未描述</t>
+  </si>
+  <si>
+    <t>弥散成像未描述</t>
+  </si>
+  <si>
+    <t>磁敏感成像未描述</t>
+  </si>
+  <si>
+    <t>股动脉</t>
+  </si>
+  <si>
+    <t>双肾上腺</t>
+  </si>
+  <si>
+    <t>主动脉、冠状动脉硬化</t>
+  </si>
+  <si>
+    <t>胰管轻度扩张</t>
+  </si>
+  <si>
+    <t>门静脉左支可见一异常区域,大小强化约1CM,形态不规则,边界不清</t>
+  </si>
+  <si>
+    <t>肺栓塞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>严重颅内出血</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>左肺下叶前基底段少许慢性炎症 中术语“左肺下叶前基底段”不标准;左肺下叶前基底段少许斑片影 中术语“左肺下叶前基底段”不标准</t>
+  </si>
+  <si>
+    <t>肝实质密度均匀,未见异常密度影;考虑多囊肝改变</t>
+  </si>
+  <si>
+    <t>肝脏形态正常;肝边缘欠光整</t>
+  </si>
+  <si>
+    <t>增强未描述;肝左叶较小;肝脏未见异常密度影;肝左叶较小;双肾及肾上腺未见明显异常;附见右肾小囊肿</t>
+  </si>
+  <si>
+    <t>胰腺形态大小、密度未见异常;相邻胰腺头部略增大</t>
+  </si>
+  <si>
+    <t>右侧胸腔未见积液;右侧胸腔积液</t>
+  </si>
+  <si>
+    <t>[描述]左肺上叶前段另见钙化结节;[结论]右肺上叶前段钙化结节</t>
+  </si>
+  <si>
+    <t>[描述]右肺下叶前内基底段见不规则团片影;[结论]左肺下叶前内基底段不规则团片影</t>
+  </si>
+  <si>
+    <t>[描述]右髂窝见肾形软组织影伴钙化;[结论]左髂窝软组织影伴多发钙化</t>
+  </si>
+  <si>
+    <t>[描述]右肾上极见低密度影;[结论]左肾上极低密度灶</t>
+  </si>
+  <si>
+    <t>[描述]左侧上颌骨内可见一不规则形高密度影;[结论]考虑右侧上颌骨占位性病变</t>
+  </si>
+  <si>
+    <t>鼻窦;[描述]鼻腔左侧钩突(位于中鼻甲前上方的骨性突起)形态异常其尖端部分可见一局限性软组织密度影;[结论]鼻腔右侧钩突肥大并伴有软组织肿块</t>
   </si>
 </sst>
 </file>
@@ -942,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -983,7 +985,7 @@
         <v>102</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.15">
@@ -1006,7 +1008,7 @@
         <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
@@ -1029,7 +1031,7 @@
         <v>102</v>
       </c>
       <c r="H4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
@@ -1052,7 +1054,7 @@
         <v>102</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -1075,7 +1077,7 @@
         <v>102</v>
       </c>
       <c r="H6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
@@ -1098,7 +1100,7 @@
         <v>103</v>
       </c>
       <c r="H7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -1121,7 +1123,7 @@
         <v>103</v>
       </c>
       <c r="H8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
@@ -1144,7 +1146,7 @@
         <v>102</v>
       </c>
       <c r="H9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -1167,7 +1169,7 @@
         <v>102</v>
       </c>
       <c r="H10" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
@@ -1190,7 +1192,7 @@
         <v>102</v>
       </c>
       <c r="H11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -1213,7 +1215,7 @@
         <v>102</v>
       </c>
       <c r="H12" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
@@ -1236,7 +1238,7 @@
         <v>103</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
@@ -1259,7 +1261,7 @@
         <v>102</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
@@ -1282,7 +1284,7 @@
         <v>102</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -1305,7 +1307,7 @@
         <v>102</v>
       </c>
       <c r="H16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.15">
@@ -1328,7 +1330,7 @@
         <v>102</v>
       </c>
       <c r="H17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.15">
@@ -1351,7 +1353,7 @@
         <v>102</v>
       </c>
       <c r="H18" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.15">
@@ -1374,7 +1376,7 @@
         <v>102</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.15">
@@ -1397,7 +1399,7 @@
         <v>102</v>
       </c>
       <c r="H20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.15">
@@ -1420,7 +1422,7 @@
         <v>102</v>
       </c>
       <c r="H21" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.15">
@@ -1443,7 +1445,7 @@
         <v>102</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.15">
@@ -1466,7 +1468,7 @@
         <v>102</v>
       </c>
       <c r="H23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.15">
@@ -1489,7 +1491,7 @@
         <v>102</v>
       </c>
       <c r="H24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.15">
@@ -1512,7 +1514,7 @@
         <v>102</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.15">
@@ -1535,7 +1537,7 @@
         <v>102</v>
       </c>
       <c r="H26" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.15">
@@ -1558,7 +1560,7 @@
         <v>102</v>
       </c>
       <c r="H27" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.15">
@@ -1581,7 +1583,7 @@
         <v>103</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.15">
@@ -1604,7 +1606,7 @@
         <v>102</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.15">
@@ -1627,7 +1629,7 @@
         <v>102</v>
       </c>
       <c r="H30" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.15">
@@ -1650,7 +1652,7 @@
         <v>102</v>
       </c>
       <c r="H31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
